--- a/ru/downloads/data-excel/1.b.1.1.xlsx
+++ b/ru/downloads/data-excel/1.b.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0094B8-E555-47EA-900E-8883C6AE8D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -123,7 +124,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -249,7 +250,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -260,9 +261,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal 17" xfId="1"/>
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -534,15 +535,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>20</v>
       </c>
@@ -553,7 +554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
@@ -564,7 +565,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -579,8 +580,9 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-    </row>
-    <row r="4" spans="1:14" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O3" s="4"/>
+    </row>
+    <row r="4" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>0</v>
       </c>
@@ -623,8 +625,11 @@
       <c r="N4" s="3">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -635,7 +640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -678,8 +683,11 @@
       <c r="N6" s="7">
         <v>75.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="1">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -722,8 +730,11 @@
       <c r="N7" s="7">
         <v>24.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="1">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -745,7 +756,7 @@
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
     </row>
-    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -788,8 +799,11 @@
       <c r="N9" s="7">
         <v>31.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="1">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -832,8 +846,11 @@
       <c r="N10" s="7">
         <v>68.900000000000006</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="1">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -855,7 +872,7 @@
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
     </row>
-    <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
@@ -898,8 +915,11 @@
       <c r="N12" s="7">
         <v>76.7</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="1">
+        <v>92.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
@@ -942,8 +962,11 @@
       <c r="N13" s="7">
         <v>23.3</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="1">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -965,7 +988,7 @@
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
     </row>
-    <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1008,8 +1031,11 @@
       <c r="N15" s="7">
         <v>89</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O15" s="1">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1052,8 +1078,11 @@
       <c r="N16" s="7">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>30</v>
       </c>
@@ -1075,7 +1104,7 @@
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
     </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1118,8 +1147,11 @@
       <c r="N18" s="7">
         <v>48.3</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O18" s="1">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>26</v>
       </c>
@@ -1162,8 +1194,11 @@
       <c r="N19" s="8">
         <v>51.7</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="8">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>31</v>
       </c>
@@ -1180,7 +1215,7 @@
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1188,7 +1223,7 @@
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -1196,7 +1231,7 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1204,7 +1239,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1212,7 +1247,7 @@
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -1220,7 +1255,7 @@
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1228,7 +1263,7 @@
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -1236,7 +1271,7 @@
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -1244,7 +1279,7 @@
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
